--- a/KatalonData/ABPTestData/NormalizedSharedData.xlsx
+++ b/KatalonData/ABPTestData/NormalizedSharedData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476640\Documents\VPS-Katalon\KatalonData\ABPTestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99EC052-7F75-4953-88FC-A76FE1AC2612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE741DEC-B21B-4169-A1A6-4A2CA5AB9B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BCCB990F-B3AB-4CDA-A16C-818C7712AEED}"/>
   </bookViews>
   <sheets>
     <sheet name="NameData" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="86">
   <si>
     <t>ID</t>
   </si>
@@ -200,9 +200,6 @@
   </si>
   <si>
     <t>65987541</t>
-  </si>
-  <si>
-    <t>65239412</t>
   </si>
   <si>
     <t>698 manadan terrace</t>
@@ -730,13 +727,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -761,7 +758,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -772,7 +769,7 @@
         <v>25</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -785,10 +782,10 @@
         <v>49</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -984,13 +981,13 @@
         <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -1010,7 +1007,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1021,7 +1018,7 @@
         <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>50</v>
@@ -1030,7 +1027,7 @@
         <v>45</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1047,10 +1044,10 @@
         <v>50</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1075,16 +1072,16 @@
         <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1092,33 +1089,33 @@
         <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>50</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1148,7 +1145,7 @@
         <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -1156,13 +1153,13 @@
         <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -1170,13 +1167,13 @@
         <v>46</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -1216,10 +1213,10 @@
         <v>45</v>
       </c>
       <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1227,7 +1224,7 @@
         <v>46</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1240,7 +1237,7 @@
         <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1278,13 +1275,13 @@
         <v>45</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
